--- a/data/trans_orig/P1407-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2012</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>58824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66728</t>
+          <t>65890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>961444</t>
+          <t>961039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>972498</t>
+          <t>972221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1276043</t>
+          <t>1277790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1303643</t>
+          <t>1303801</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2244529</t>
+          <t>2245367</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2272421</t>
+          <t>2272850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31547</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>34677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1955896</t>
+          <t>1955821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962979</t>
+          <t>1962982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1723045</t>
+          <t>1723347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1742764</t>
+          <t>1743393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3682799</t>
+          <t>3683872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3704563</t>
+          <t>3704453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474904</t>
+          <t>476173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442325</t>
+          <t>444507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455689</t>
+          <t>455694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>922969</t>
+          <t>922966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936588</t>
+          <t>936586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56383</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90565</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65595</t>
+          <t>62685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99972</t>
+          <t>101043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3401370</t>
+          <t>3401025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3414727</t>
+          <t>3414621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3459272</t>
+          <t>3459383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3493454</t>
+          <t>3494195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6869647</t>
+          <t>6868576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6904024</t>
+          <t>6906934</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de estreñimiento crónico en 2016</t>
+          <t>Población con diagnóstico de estreñimiento crónico en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>25942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52257</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61930</t>
+          <t>64056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>736207</t>
+          <t>737046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>749653</t>
+          <t>749407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>942403</t>
+          <t>944136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>968520</t>
+          <t>968718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1687077</t>
+          <t>1684951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1715080</t>
+          <t>1713518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>21641</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>27636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2065700</t>
+          <t>2065477</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074494</t>
+          <t>2074495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1966836</t>
+          <t>1966659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1981214</t>
+          <t>1981438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4038369</t>
+          <t>4037049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4054727</t>
+          <t>4054197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21360</t>
+          <t>20923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539200</t>
+          <t>538971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531212</t>
+          <t>531618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545659</t>
+          <t>545294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1074667</t>
+          <t>1075104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090525</t>
+          <t>1090920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27343</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>44460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76575</t>
+          <t>77057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>58595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94000</t>
+          <t>95244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3350275</t>
+          <t>3349919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3367250</t>
+          <t>3367586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3455525</t>
+          <t>3455043</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3487773</t>
+          <t>3487640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6815718</t>
+          <t>6814474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6852105</t>
+          <t>6851123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1407-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1407-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58824</t>
+          <t>58542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>38861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65890</t>
+          <t>66667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>961039</t>
+          <t>961462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>972221</t>
+          <t>972489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1277790</t>
+          <t>1278072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1303801</t>
+          <t>1304593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2245367</t>
+          <t>2244590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2272850</t>
+          <t>2272396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>33242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34677</t>
+          <t>35426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1955821</t>
+          <t>1955936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962982</t>
+          <t>1962977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1723347</t>
+          <t>1721350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1743393</t>
+          <t>1742797</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3683872</t>
+          <t>3683123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3704453</t>
+          <t>3703656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16847</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476173</t>
+          <t>476175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444507</t>
+          <t>442789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455694</t>
+          <t>455730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>922966</t>
+          <t>923846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936586</t>
+          <t>936723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>56118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>90645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>64690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101043</t>
+          <t>102341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3401025</t>
+          <t>3400640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3414621</t>
+          <t>3414730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3459383</t>
+          <t>3459192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3494195</t>
+          <t>3493719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6868576</t>
+          <t>6867278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6906934</t>
+          <t>6904929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>51797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64056</t>
+          <t>62793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>737046</t>
+          <t>735877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>749407</t>
+          <t>749724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>944136</t>
+          <t>942863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>968718</t>
+          <t>968296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1684951</t>
+          <t>1686214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1713518</t>
+          <t>1715287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27636</t>
+          <t>27989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2065477</t>
+          <t>2065425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074495</t>
+          <t>2074486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1966659</t>
+          <t>1966161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1981438</t>
+          <t>1981201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4037049</t>
+          <t>4036696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4054197</t>
+          <t>4054439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538971</t>
+          <t>539122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531618</t>
+          <t>530990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545294</t>
+          <t>545345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075104</t>
+          <t>1075226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090920</t>
+          <t>1090993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>9772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27699</t>
+          <t>26846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44460</t>
+          <t>44280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77057</t>
+          <t>77119</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58595</t>
+          <t>58525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95244</t>
+          <t>95518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3349919</t>
+          <t>3350772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3367586</t>
+          <t>3367846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3455043</t>
+          <t>3454981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3487640</t>
+          <t>3487820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6814474</t>
+          <t>6814200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6851123</t>
+          <t>6851193</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
